--- a/artfynd/A 7138-2025 artfynd.xlsx
+++ b/artfynd/A 7138-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>121150363</v>
       </c>
       <c r="B2" t="n">
-        <v>91989</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
